--- a/mosip_master/xlsx/reg_center_type.xlsx
+++ b/mosip_master/xlsx/reg_center_type.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6920"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="reg_center_type" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
   <si>
     <t>code</t>
   </si>
@@ -74,28 +74,13 @@
     <t>eng</t>
   </si>
   <si>
-    <t>System</t>
-  </si>
-  <si>
-    <t>NULL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">नियमित </t>
-  </si>
-  <si>
-    <t>नियमित पंजीकरण केंद्र</t>
-  </si>
-  <si>
-    <t>hin</t>
-  </si>
-  <si>
-    <t>Régulière</t>
-  </si>
-  <si>
-    <t>Centre d'inscription régulier</t>
-  </si>
-  <si>
-    <t>fra</t>
+    <t>t</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>f</t>
   </si>
   <si>
     <t>NEWREG</t>
@@ -105,9 +90,6 @@
   </si>
   <si>
     <t>Testing Purpose</t>
-  </si>
-  <si>
-    <t>globaladmin</t>
   </si>
   <si>
     <t>vishal</t>
@@ -1273,11 +1255,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14.5" outlineLevelRow="5"/>
-  <cols>
-    <col min="3" max="3" width="26.5454545454545" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
@@ -1314,7 +1292,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1327,167 +1305,84 @@
       <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="b">
-        <v>1</v>
+      <c r="E2" t="s">
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1">
-        <v>45526.6013926323</v>
-      </c>
-      <c r="H2" t="s">
+        <v>45667.2623817337</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" t="s">
-        <v>16</v>
+      <c r="G3" s="1">
+        <v>45667.2623817337</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="1">
+        <v>45636.2319483565</v>
+      </c>
+      <c r="J3" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="1">
-        <v>45526.6013926323</v>
-      </c>
-      <c r="H3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" s="1">
-        <v>45526.6013926323</v>
-      </c>
-      <c r="H4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" t="s">
-        <v>16</v>
+        <v>45667.2623817337</v>
+      </c>
+      <c r="J4" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="1">
-        <v>45636.2292514052</v>
-      </c>
-      <c r="H5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="1">
-        <v>45636.231948358</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="s">
-        <v>16</v>
-      </c>
+    <row r="5" spans="7:9">
+      <c r="G5" s="1"/>
+      <c r="H5"/>
+      <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="1">
-        <v>45526.6013926323</v>
-      </c>
-      <c r="H6" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" t="s">
-        <v>16</v>
-      </c>
+    <row r="6" spans="7:7">
+      <c r="G6" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
